--- a/reporte_Mapas.xlsx
+++ b/reporte_Mapas.xlsx
@@ -580,8 +580,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="30" customWidth="1" style="16" min="1" max="1"/>
-    <col width="25" customWidth="1" style="16" min="2" max="2"/>
-    <col width="45" customWidth="1" style="16" min="3" max="3"/>
+    <col width="45" customWidth="1" style="16" min="2" max="2"/>
+    <col width="35" customWidth="1" style="16" min="3" max="3"/>
     <col width="115" customWidth="1" style="16" min="4" max="4"/>
     <col width="23" customWidth="1" style="16" min="5" max="6"/>
     <col width="18" customWidth="1" style="16" min="7" max="7"/>
@@ -606,7 +606,7 @@
         <is>
           <t>Empresa: BBVA
 Usuario: Uriel Meneses
-Fecha de descarga: 11-03-2026
+Fecha de descarga: 12-03-2026
 Descarga por Fecha de publicación del 2026-01-01 al 2026-01-31</t>
         </is>
       </c>
